--- a/data/负载归一24/河北省/节假日.xlsx
+++ b/data/负载归一24/河北省/节假日.xlsx
@@ -4,9 +4,7 @@
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\paper2\data\负荷曲线\负载归一24\河北\"/>
-    </mc:Choice>
+    <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7D26472-22E4-4164-BDBC-B814A02029F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
